--- a/artfynd/A 19847-2021 artfynd.xlsx
+++ b/artfynd/A 19847-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19847-2021 artfynd.xlsx
+++ b/artfynd/A 19847-2021 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>104412089</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404942.2523671164</v>
+        <v>404942</v>
       </c>
       <c r="R14" t="n">
-        <v>6776063.29135132</v>
+        <v>6776064</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2109,19 +2109,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2395,7 +2385,7 @@
         <v>104412034</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2440,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404876.7057518549</v>
+        <v>404876</v>
       </c>
       <c r="R17" t="n">
-        <v>6776183.55974441</v>
+        <v>6776184</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,19 +2463,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 19847-2021 artfynd.xlsx
+++ b/artfynd/A 19847-2021 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>104412089</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>104412034</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
